--- a/dados/Vendas por Produto - GERAL.xlsx
+++ b/dados/Vendas por Produto - GERAL.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>CODFILIAL</t>
   </si>
@@ -123,9 +123,6 @@
     <t>ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 FARMA C</t>
   </si>
   <si>
-    <t>1590</t>
-  </si>
-  <si>
     <t>474</t>
   </si>
   <si>
@@ -174,6 +171,12 @@
     <t>ATADURA DE CREPE 13 FIOS 15 X 1,80  PCT 12 FARMA C</t>
   </si>
   <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATADURA DE CREPE 13 FIOS 20 X 1,20  PCT 12  FARMA C </t>
+  </si>
+  <si>
     <t>423</t>
   </si>
   <si>
@@ -204,7 +207,34 @@
     <t>ATADURA DE CREPE 13 FIOS 20 X 1,80  PCT 12 FARMA C</t>
   </si>
   <si>
-    <t>174</t>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12</t>
+  </si>
+  <si>
+    <t>MED TEXTIL</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12  HOSPITALAR C</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12 FARMA C</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12   HOSPITALAR C</t>
+  </si>
+  <si>
+    <t>1599</t>
   </si>
   <si>
     <t>ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12 FARMA C</t>
@@ -216,7 +246,22 @@
     <t xml:space="preserve">ATADURA DE CREPE13 FIOS 15 X 1,80  PCT 12 </t>
   </si>
   <si>
-    <t>MED TEXTIL</t>
+    <t>1664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATADURA DE CREPE13 FIOS 20 X 1,80  PCT 12 </t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND </t>
   </si>
   <si>
     <t>158</t>
@@ -249,67 +294,46 @@
     <t>CAMPO OPERATORIO NAO ESTERIL 45X50 S/ RX - PCT 50 UND</t>
   </si>
   <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAZE  CIRCULAR NAO ESTERIL 09 FIOS </t>
+    <t>82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
   </si>
   <si>
     <t>85</t>
   </si>
   <si>
-    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 09 FIOS </t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>1822</t>
+    <t>263</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
   </si>
   <si>
-    <t>263</t>
-  </si>
-  <si>
     <t>359</t>
   </si>
   <si>
     <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS</t>
   </si>
   <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>2010</t>
+    <t>112</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 13 FIOS </t>
   </si>
   <si>
-    <t>2011</t>
+    <t>273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 13 FIOS  </t>
   </si>
   <si>
     <t>1819</t>
   </si>
   <si>
-    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 13 FIOS  </t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>299</t>
-  </si>
-  <si>
-    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS CA</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS D</t>
+    <t>297</t>
+  </si>
+  <si>
+    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS AA</t>
   </si>
   <si>
     <t>277</t>
@@ -324,24 +348,54 @@
     <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS GA</t>
   </si>
   <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS JA</t>
+    <t>286</t>
+  </si>
+  <si>
+    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS OA</t>
+  </si>
+  <si>
+    <t>1641</t>
+  </si>
+  <si>
+    <t>GAZE ESTÉRIL 09 FIOS - PCT 10 UND</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE ESTÉRIL 09 FIOS - PCT 10 UND </t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE ESTERIL 09 FIOS ULTRA TEXTIL PCT 10 UND </t>
+  </si>
+  <si>
     <t>153</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE ESTERIL 11 FIOS PCT 10 UND </t>
   </si>
   <si>
+    <t>1642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE ESTÉRIL 11FIOS -  PCT 10 UND </t>
+  </si>
+  <si>
     <t xml:space="preserve">GAZE ESTÉRIL 11FIOS - PCT 10 UND </t>
   </si>
   <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE ESTERIL 13 FIOS PCT 10 UND </t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>GAZE ESTÉRIL 13FIOS - CONVIVA - PCT 10 UND</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
   </si>
   <si>
@@ -360,25 +414,40 @@
     <t>GAZE NAO ESTÉRIL 09 FIOS - PCT 500 UND</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>GAZE NAO ESTÉRIL 09 FIOS F</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>GAZE NAO ESTÉRIL 09 FIOS G</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>GAZE NAO ESTÉRIL 09 FIOS I</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE NAO ESTÉRIL 11 FIOS </t>
+  </si>
+  <si>
     <t>339</t>
   </si>
   <si>
     <t>GAZE NAO ESTÉRIL 11 FIOS BA - PCT 500 UND</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAZE NAO ESTERIL 13 FIOS </t>
-  </si>
-  <si>
-    <t>324</t>
+    <t>326</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE NAO ESTÉRIL 13 FIOS </t>
-  </si>
-  <si>
-    <t>326</t>
   </si>
   <si>
     <t>349</t>
@@ -551,7 +620,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="8.42578125" customWidth="true"/>
@@ -622,13 +691,13 @@
         <v>16</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>759</v>
+        <v>948.75</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>40</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>30360</v>
+        <v>37950</v>
       </c>
     </row>
     <row r="3" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -654,13 +723,13 @@
         <v>22</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>880</v>
+        <v>550</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>4.185</v>
+        <v>4.24</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>3682.8</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -686,13 +755,13 @@
         <v>22</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>600</v>
+        <v>4290</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2388</v>
+        <v>17031.3</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -718,13 +787,13 @@
         <v>22</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1210</v>
+        <v>2750</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3.85</v>
+        <v>3.6668</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4658.5</v>
+        <v>10083.7</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -750,13 +819,13 @@
         <v>22</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>200</v>
+        <v>2600</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.57</v>
+        <v>4.2454</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>914</v>
+        <v>11038</v>
       </c>
     </row>
     <row r="7" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -782,13 +851,13 @@
         <v>22</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1462</v>
+        <v>602</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5.2006</v>
+        <v>5.21</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>7603.26</v>
+        <v>3136.42</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -814,13 +883,13 @@
         <v>22</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.715</v>
+        <v>4.6292</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1143</v>
+        <v>6018</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -846,13 +915,13 @@
         <v>22</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>602</v>
+        <v>448</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4.76</v>
+        <v>4.7677</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>2865.52</v>
+        <v>2135.92</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -878,13 +947,13 @@
         <v>22</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>110</v>
+        <v>1320</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>540.1</v>
+        <v>6481.2</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -895,7 +964,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>19</v>
@@ -904,19 +973,19 @@
         <v>20</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>5.195</v>
+        <v>6.58</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4571.6</v>
+        <v>5527.2</v>
       </c>
     </row>
     <row r="12" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -924,10 +993,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>19</v>
@@ -936,19 +1005,19 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1050</v>
+        <v>360</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.58</v>
+        <v>6.78</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6909</v>
+        <v>2440.8</v>
       </c>
     </row>
     <row r="13" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -956,10 +1025,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>19</v>
@@ -968,19 +1037,19 @@
         <v>20</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>90</v>
+        <v>3920</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>7.62</v>
+        <v>5.07</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>685.8</v>
+        <v>19874.4</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -988,10 +1057,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
@@ -1000,19 +1069,19 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1610</v>
+        <v>1530</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.47</v>
+        <v>5.3265</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8806.7</v>
+        <v>8149.5</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1020,10 +1089,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>19</v>
@@ -1032,19 +1101,19 @@
         <v>20</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1260</v>
+        <v>6120</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>5.8186</v>
+        <v>5.5003</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7331.4</v>
+        <v>33661.8</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1052,10 +1121,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>19</v>
@@ -1070,13 +1139,13 @@
         <v>22</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2430</v>
+        <v>720</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.5363</v>
+        <v>7.7</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>13453.2</v>
+        <v>5544</v>
       </c>
     </row>
     <row r="17" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1084,10 +1153,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>19</v>
@@ -1102,13 +1171,13 @@
         <v>22</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1860</v>
+        <v>450</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7.6629</v>
+        <v>7.92</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>14253</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1116,10 +1185,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>19</v>
@@ -1128,19 +1197,19 @@
         <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4647</v>
+        <v>2400</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7.454</v>
+        <v>7.04</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>34638.96</v>
+        <v>16896</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1148,10 +1217,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>19</v>
@@ -1160,19 +1229,19 @@
         <v>20</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>150</v>
+        <v>1610</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>8.425</v>
+        <v>6.757</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1263.75</v>
+        <v>10878.7</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1180,10 +1249,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>19</v>
@@ -1198,13 +1267,13 @@
         <v>22</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2288</v>
+        <v>2392</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7.015</v>
+        <v>6.7183</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>16050.32</v>
+        <v>16070.08</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1212,10 +1281,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>19</v>
@@ -1230,13 +1299,13 @@
         <v>22</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1050</v>
+        <v>1750</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>7.5393</v>
+        <v>6.648</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>7916.3</v>
+        <v>11634</v>
       </c>
     </row>
     <row r="22" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1244,10 +1313,10 @@
         <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>19</v>
@@ -1262,13 +1331,13 @@
         <v>22</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1540</v>
+        <v>396</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>9.99</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>15384.6</v>
+        <v>3956.04</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1276,10 +1345,10 @@
         <v>10</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>19</v>
@@ -1294,13 +1363,13 @@
         <v>22</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1900</v>
+        <v>360</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>10.1685</v>
+        <v>10.13</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>19320.1</v>
+        <v>3646.8</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1308,10 +1377,10 @@
         <v>10</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>19</v>
@@ -1326,13 +1395,13 @@
         <v>22</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>70</v>
+        <v>1920</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10.3</v>
+        <v>8.8572</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>721</v>
+        <v>17005.8</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1340,10 +1409,10 @@
         <v>10</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>19</v>
@@ -1352,19 +1421,19 @@
         <v>20</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>14.74</v>
+        <v>12.32</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>1886.72</v>
+        <v>431.2</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1372,10 +1441,10 @@
         <v>10</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>19</v>
@@ -1384,17 +1453,19 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4"/>
+        <v>210</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>10.74</v>
+      </c>
       <c r="J26" s="4" t="n">
-        <v>0</v>
+        <v>2255.4</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1402,10 +1473,10 @@
         <v>10</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>19</v>
@@ -1414,19 +1485,19 @@
         <v>20</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>23400</v>
+        <v>100</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4.8251</v>
+        <v>11.95</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>112906.5</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1434,10 +1505,10 @@
         <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>19</v>
@@ -1446,19 +1517,19 @@
         <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>28500</v>
+        <v>84</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.4529</v>
+        <v>14.3</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>126907.5</v>
+        <v>1201.2</v>
       </c>
     </row>
     <row r="29" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1466,10 +1537,10 @@
         <v>10</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>19</v>
@@ -1484,13 +1555,13 @@
         <v>22</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1056</v>
+        <v>280</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>49.2805</v>
+        <v>13.5629</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>52040.16</v>
+        <v>3797.6</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1498,10 +1569,10 @@
         <v>10</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>19</v>
@@ -1510,19 +1581,19 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5472</v>
+        <v>70</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>45.0622</v>
+        <v>9.1784</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>246580.32</v>
+        <v>642.488</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1530,10 +1601,10 @@
         <v>10</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>19</v>
@@ -1542,19 +1613,19 @@
         <v>20</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>48</v>
+        <v>11.7832</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>576</v>
+        <v>706.992</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1562,10 +1633,10 @@
         <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>19</v>
@@ -1574,19 +1645,19 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1224</v>
+        <v>17400</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9</v>
+        <v>2.5931</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11016</v>
+        <v>45120</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1594,10 +1665,10 @@
         <v>10</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>19</v>
@@ -1612,13 +1683,13 @@
         <v>22</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>6120</v>
+        <v>300</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>13.2845</v>
+        <v>2.8</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>81301.32</v>
+        <v>840</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1626,10 +1697,10 @@
         <v>10</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>19</v>
@@ -1644,13 +1715,13 @@
         <v>22</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>320</v>
+        <v>21900</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>27.9</v>
+        <v>4.411</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8928</v>
+        <v>96600</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1658,10 +1729,10 @@
         <v>10</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>19</v>
@@ -1670,19 +1741,19 @@
         <v>20</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>320</v>
+        <v>48150</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>28.5</v>
+        <v>4.5683</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>9120</v>
+        <v>219963</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1690,10 +1761,10 @@
         <v>10</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>19</v>
@@ -1708,13 +1779,13 @@
         <v>22</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1440</v>
+        <v>6504</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>14.6513</v>
+        <v>38.6632</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>21097.8</v>
+        <v>251465.1408</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1722,10 +1793,10 @@
         <v>10</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>19</v>
@@ -1734,19 +1805,19 @@
         <v>20</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1800</v>
+        <v>2868</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>13</v>
+        <v>43.5067</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>23400</v>
+        <v>124777.2</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1754,10 +1825,10 @@
         <v>10</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>19</v>
@@ -1772,13 +1843,13 @@
         <v>22</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>60</v>
+        <v>588</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>15.67</v>
+        <v>45.6608</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>940.2</v>
+        <v>26848.56</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1786,10 +1857,10 @@
         <v>10</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>19</v>
@@ -1798,19 +1869,19 @@
         <v>20</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>19.85</v>
+        <v>10.8</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>992.5</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="40" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1818,10 +1889,10 @@
         <v>10</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>19</v>
@@ -1830,19 +1901,19 @@
         <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>300</v>
+        <v>12060</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>51.3</v>
+        <v>13.7526</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>15390</v>
+        <v>165855.96</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1850,10 +1921,10 @@
         <v>10</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>19</v>
@@ -1862,19 +1933,19 @@
         <v>20</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1620</v>
+        <v>150</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>15.4433</v>
+        <v>20.99</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>25018.2</v>
+        <v>3148.5</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1882,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>19</v>
@@ -1900,13 +1971,13 @@
         <v>22</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1224</v>
+        <v>2196</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13.9</v>
+        <v>12.9798</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>17013.6</v>
+        <v>28503.72</v>
       </c>
     </row>
     <row r="43" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1914,10 +1985,10 @@
         <v>10</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>19</v>
@@ -1926,19 +1997,19 @@
         <v>20</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>60</v>
+        <v>324</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>23.88</v>
+        <v>12.5</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1432.8</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="44" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1946,10 +2017,10 @@
         <v>10</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>19</v>
@@ -1958,19 +2029,19 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>320</v>
+        <v>864</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>29</v>
+        <v>13.6667</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>9280</v>
+        <v>11808</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1978,10 +2049,10 @@
         <v>10</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>19</v>
@@ -1990,19 +2061,19 @@
         <v>20</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>10020</v>
+        <v>36</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>135270</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2010,10 +2081,10 @@
         <v>10</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>19</v>
@@ -2022,19 +2093,19 @@
         <v>20</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19.88</v>
+        <v>28.8</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>4771.2</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="47" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2042,10 +2113,10 @@
         <v>10</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>19</v>
@@ -2060,13 +2131,13 @@
         <v>22</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>5060</v>
+        <v>10500</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>16.7258</v>
+        <v>13.0714</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>84632.8</v>
+        <v>137250</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2074,10 +2145,10 @@
         <v>10</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>19</v>
@@ -2092,13 +2163,13 @@
         <v>22</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>104000</v>
+        <v>270</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.3716</v>
+        <v>19.7899</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>38650</v>
+        <v>5343.264</v>
       </c>
     </row>
     <row r="49" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2106,10 +2177,10 @@
         <v>10</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>19</v>
@@ -2118,19 +2189,19 @@
         <v>20</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>40000</v>
+        <v>1125</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.4171</v>
+        <v>19.9689</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>16684</v>
+        <v>22465</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2138,10 +2209,10 @@
         <v>10</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>19</v>
@@ -2150,19 +2221,19 @@
         <v>20</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>567000</v>
+        <v>1000</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.3713</v>
+        <v>0.6</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>210516</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2170,10 +2241,10 @@
         <v>10</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>19</v>
@@ -2188,13 +2259,13 @@
         <v>22</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1720000</v>
+        <v>148000</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.3345</v>
+        <v>0.3685</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>575420</v>
+        <v>54540</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2202,10 +2273,10 @@
         <v>10</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>19</v>
@@ -2214,19 +2285,19 @@
         <v>20</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.6227</v>
+        <v>0.4312</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>6850</v>
+        <v>862.4</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2234,10 +2305,10 @@
         <v>10</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>19</v>
@@ -2246,19 +2317,19 @@
         <v>20</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>9792</v>
+        <v>5000</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>6.924</v>
+        <v>0.423</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>67799.52</v>
+        <v>2115.2</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2266,10 +2337,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>19</v>
@@ -2278,19 +2349,19 @@
         <v>20</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>5400</v>
+        <v>10000</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>14.626</v>
+        <v>0.62</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>78980.4</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2298,10 +2369,10 @@
         <v>10</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>19</v>
@@ -2310,19 +2381,19 @@
         <v>20</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>1152</v>
+        <v>439000</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>16.9125</v>
+        <v>0.3793</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>19483.2</v>
+        <v>166520</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2330,10 +2401,10 @@
         <v>10</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>19</v>
@@ -2342,19 +2413,19 @@
         <v>20</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>19</v>
+        <v>0.486</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>11400</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2362,10 +2433,10 @@
         <v>10</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>19</v>
@@ -2374,19 +2445,19 @@
         <v>20</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>1020</v>
+        <v>14000</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>8.85</v>
+        <v>0.49</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>9027</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2394,10 +2465,10 @@
         <v>10</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>19</v>
@@ -2412,13 +2483,13 @@
         <v>22</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>300</v>
+        <v>1841000</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11.85</v>
+        <v>0.3717</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>3555</v>
+        <v>684250</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2426,10 +2497,10 @@
         <v>10</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>19</v>
@@ -2438,19 +2509,19 @@
         <v>20</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>3680</v>
+        <v>13000</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>15.7219</v>
+        <v>0.6477</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>57856.64</v>
+        <v>8420</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2458,10 +2529,10 @@
         <v>10</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>19</v>
@@ -2476,31 +2547,319 @@
         <v>22</v>
       </c>
       <c r="H60" s="4" t="n">
+        <v>21240</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>6.0609</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>128733.84</v>
+      </c>
+    </row>
+    <row r="61" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>2080</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>14.2917</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>29726.768</v>
+      </c>
+    </row>
+    <row r="62" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>6540</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>47938.2</v>
+      </c>
+    </row>
+    <row r="63" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="64" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>10.4322</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>9389</v>
+      </c>
+    </row>
+    <row r="65" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I60" s="4" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="61" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="9" t="n">
-        <v>2579588</v>
-      </c>
-      <c r="I61" s="9" t="n">
-        <v>784.0124</v>
-      </c>
-      <c r="J61" s="9" t="n">
-        <v>2292895.29</v>
+      <c r="I65" s="6" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="66" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>15.912</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>3055.104</v>
+      </c>
+    </row>
+    <row r="67" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A67" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="68" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>20.8815</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>6013.8624</v>
+      </c>
+    </row>
+    <row r="69" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A69" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>13.8461</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>15923</v>
+      </c>
+    </row>
+    <row r="70" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A70" s="7"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="9" t="n">
+        <v>2674863.75</v>
+      </c>
+      <c r="I70" s="9" t="n">
+        <v>706.1151</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>2592196.6592</v>
       </c>
     </row>
   </sheetData>

--- a/dados/Vendas por Produto - GERAL.xlsx
+++ b/dados/Vendas por Produto - GERAL.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>CODFILIAL</t>
   </si>
@@ -75,12 +75,6 @@
     <t>ULTRA TEXTIL</t>
   </si>
   <si>
-    <t>416</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 10 X 1,20  PCT 12 HOSPITALAR E</t>
-  </si>
-  <si>
     <t>1661</t>
   </si>
   <si>
@@ -108,18 +102,12 @@
     <t>ATADURA DE CREPE 13 FIOS 10 X 1,80  PCT 12 - FARMA C</t>
   </si>
   <si>
-    <t>480</t>
+    <t>1590</t>
   </si>
   <si>
     <t>ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 FARMA C</t>
   </si>
   <si>
-    <t>477</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 12 X 1,20  PCT 12 HOSPITALAR E</t>
-  </si>
-  <si>
     <t>1662</t>
   </si>
   <si>
@@ -159,18 +147,6 @@
     <t xml:space="preserve">ATADURA DE CREPE 13 FIOS 15 X 1,20  PCT 12 FARMA C </t>
   </si>
   <si>
-    <t>1618</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 15 X 1,20  PCT 12 HOSP. C</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 15 X 1,20  PCT 12 HOSPITALAR E</t>
-  </si>
-  <si>
     <t>421</t>
   </si>
   <si>
@@ -201,24 +177,12 @@
     <t>ATADURA DE CREPE 13 FIOS 20 X 1,20  PCT 12  HOSPITALAR C</t>
   </si>
   <si>
-    <t>424</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 20 X 1,20  PCT 12  HOSPITALAR E</t>
-  </si>
-  <si>
     <t>1593</t>
   </si>
   <si>
     <t>ATADURA DE CREPE 13 FIOS 20 X 1,20  PCT 12 FARMA C</t>
   </si>
   <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 20 X 1,20  PCT 12 FARMA E</t>
-  </si>
-  <si>
     <t>425</t>
   </si>
   <si>
@@ -237,60 +201,51 @@
     <t>ATADURA DE CREPE 13 FIOS 20 X 1,80  PCT 12 FARMA C</t>
   </si>
   <si>
-    <t>427</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12  HOSPITALAR C</t>
-  </si>
-  <si>
-    <t>428</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12  HOSPITALAR E</t>
-  </si>
-  <si>
     <t>1594</t>
   </si>
   <si>
     <t>ATADURA DE CREPE 13 FIOS 30 X 1,20  PCT 12 FARMA C</t>
   </si>
   <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12   HOSPITALAR C</t>
+  </si>
+  <si>
     <t>1599</t>
   </si>
   <si>
     <t>ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12 FARMA C</t>
   </si>
   <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 30 X 1,80  PCT 12 FARMA E</t>
-  </si>
-  <si>
-    <t>1644</t>
-  </si>
-  <si>
-    <t>ATADURA DE CREPE 13 FIOS 8 X 1,20  PCT 12 FARMA C</t>
-  </si>
-  <si>
     <t>1663</t>
   </si>
   <si>
     <t xml:space="preserve">ATADURA DE CREPE13 FIOS 15 X 1,80  PCT 12 </t>
   </si>
   <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND</t>
+    <t>1664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATADURA DE CREPE13 FIOS 20 X 1,80  PCT 12 </t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO OPERATORIO ESTERIL 25X28 - PCT 2 UND </t>
+  </si>
+  <si>
+    <t>1640</t>
+  </si>
+  <si>
+    <t>CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND</t>
   </si>
   <si>
     <t>158</t>
   </si>
   <si>
-    <t>CAMPO OPERATORIO ESTERIL 25X28 - PCT 5 UND</t>
-  </si>
-  <si>
     <t>2073</t>
   </si>
   <si>
@@ -306,18 +261,18 @@
     <t>CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50</t>
   </si>
   <si>
+    <t>1209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50 </t>
+  </si>
+  <si>
     <t>155</t>
   </si>
   <si>
     <t>CAMPO OPERATORIO NAO ESTERIL 45X50 - PCT 50 UND</t>
   </si>
   <si>
-    <t>1797</t>
-  </si>
-  <si>
-    <t>CAMPO OPERATORIO NAO ESTERIL 45X50 S/ RX - PCT 50 UND</t>
-  </si>
-  <si>
     <t>84</t>
   </si>
   <si>
@@ -333,13 +288,25 @@
     <t>2070</t>
   </si>
   <si>
-    <t>132</t>
+    <t>90</t>
+  </si>
+  <si>
+    <t>GAZE CIRCULAR NAO ESTERIL 09 FIOS J</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
   </si>
   <si>
     <t>263</t>
   </si>
   <si>
-    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 11 FIOS </t>
+    <t>294</t>
+  </si>
+  <si>
+    <t>1687</t>
   </si>
   <si>
     <t>276</t>
@@ -351,19 +318,16 @@
     <t>359</t>
   </si>
   <si>
-    <t>1637</t>
-  </si>
-  <si>
-    <t>1819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 13 FIOS  </t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS D</t>
+    <t>1962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZE CIRCULAR NAO ESTERIL 13 FIOS </t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS CA</t>
   </si>
   <si>
     <t>277</t>
@@ -384,18 +348,6 @@
     <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS JA</t>
   </si>
   <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>GAZE CIRCULAR NAO ESTERIL 13 FIOS OA</t>
-  </si>
-  <si>
-    <t>1641</t>
-  </si>
-  <si>
-    <t>GAZE ESTÉRIL 09 FIOS - PCT 10 UND</t>
-  </si>
-  <si>
     <t xml:space="preserve">GAZE ESTÉRIL 09 FIOS - PCT 10 UND </t>
   </si>
   <si>
@@ -423,6 +375,18 @@
     <t xml:space="preserve">GAZE ESTERIL 13 FIOS PCT 10 UND </t>
   </si>
   <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>GAZE ESTÉRIL 13FIOS - CONVIVA - PCT 10 UND</t>
+  </si>
+  <si>
+    <t>730</t>
+  </si>
+  <si>
+    <t>GAZE ESTÉRIL 13FIOS - MEDLIFE - PCT 10 UND</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAZE ESTÉRIL 13FIOS - PCT 10 UND </t>
   </si>
   <si>
@@ -435,52 +399,55 @@
     <t xml:space="preserve">GAZE NAO ESTÉRIL 09 FIOS </t>
   </si>
   <si>
+    <t>2090</t>
+  </si>
+  <si>
     <t>51</t>
   </si>
   <si>
     <t>GAZE NAO ESTÉRIL 09 FIOS - PCT 500 UND</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>GAZE NAO ESTÉRIL 09 FIOS I</t>
-  </si>
-  <si>
-    <t>313</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>GAZE NAO ESTÉRIL 09 FIOS F</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>GAZE NAO ESTÉRIL 09 FIOS N</t>
+  </si>
+  <si>
+    <t>2091</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE NAO ESTÉRIL 11 FIOS </t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>339</t>
   </si>
   <si>
     <t>GAZE NAO ESTÉRIL 11 FIOS BA - PCT 500 UND</t>
   </si>
   <si>
-    <t>2080</t>
+    <t>326</t>
   </si>
   <si>
     <t xml:space="preserve">GAZE NAO ESTÉRIL 13 FIOS </t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>2072</t>
-  </si>
-  <si>
     <t>349</t>
   </si>
   <si>
     <t>GAZE NAO ESTÉRIL 13 FIOS  - PCT 500 UND</t>
   </si>
   <si>
-    <t>2063</t>
+    <t>1959</t>
   </si>
   <si>
     <t>GAZE NAO ESTÉRIL 13 FIOS - PCT 500 UND</t>
@@ -650,7 +617,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="8.42578125" customWidth="true"/>
@@ -724,10 +691,10 @@
         <v>330</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>3.97</v>
+        <v>4.0767</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>1310.1</v>
+        <v>1345.3</v>
       </c>
     </row>
     <row r="3" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -753,13 +720,13 @@
         <v>16</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>660</v>
+        <v>1100</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>4.1294</v>
+        <v>3.823</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2725.404</v>
+        <v>4205.3</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -779,19 +746,19 @@
         <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4.5</v>
+        <v>6.47</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1800</v>
+        <v>6987.6</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -799,10 +766,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>13</v>
@@ -811,19 +778,19 @@
         <v>14</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>180</v>
+        <v>572</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>6.99</v>
+        <v>5.4</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1258.2</v>
+        <v>3088.8</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -849,13 +816,13 @@
         <v>16</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>440</v>
+        <v>1290</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.4</v>
+        <v>5.242</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2376</v>
+        <v>6762.18</v>
       </c>
     </row>
     <row r="7" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -875,19 +842,19 @@
         <v>14</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>774</v>
+        <v>3300</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5.2144</v>
+        <v>5.4888</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4035.98</v>
+        <v>18113</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -913,13 +880,13 @@
         <v>16</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6000</v>
+        <v>990</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.4791</v>
+        <v>4.91</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>26874.48</v>
+        <v>4860.9</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -939,19 +906,19 @@
         <v>14</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>3.38</v>
+        <v>8.008</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>371.8</v>
+        <v>6406.4</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -977,13 +944,13 @@
         <v>16</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>176</v>
+        <v>1190</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.57</v>
+        <v>5.5318</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>980.32</v>
+        <v>6582.8</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1003,19 +970,19 @@
         <v>14</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>80</v>
+        <v>640</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8.9</v>
+        <v>6.84</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>712</v>
+        <v>4377.6</v>
       </c>
     </row>
     <row r="12" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1026,7 +993,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>13</v>
@@ -1035,19 +1002,19 @@
         <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>210</v>
+        <v>2700</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.58</v>
+        <v>7.1173</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1381.8</v>
+        <v>19216.8</v>
       </c>
     </row>
     <row r="13" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1055,10 +1022,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>13</v>
@@ -1073,13 +1040,13 @@
         <v>16</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>480</v>
+        <v>1960</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>6.84</v>
+        <v>4.9986</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>3283.2</v>
+        <v>9797.2</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1087,11 +1054,11 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="D14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1105,13 +1072,13 @@
         <v>16</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.991</v>
+        <v>6.0804</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>6291.9</v>
+        <v>547.236</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1137,13 +1104,13 @@
         <v>16</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1120</v>
+        <v>1044</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>5.1513</v>
+        <v>5.64</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>5769.4</v>
+        <v>5888.16</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1163,19 +1130,19 @@
         <v>14</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1260</v>
+        <v>1440</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.4836</v>
+        <v>7.6421</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>6909.3</v>
+        <v>11004.6</v>
       </c>
     </row>
     <row r="17" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1201,13 +1168,13 @@
         <v>16</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1980</v>
+        <v>1200</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>5.3673</v>
+        <v>6.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>10627.2</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1233,13 +1200,13 @@
         <v>16</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>70</v>
+        <v>4650</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5.47</v>
+        <v>7.8058</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>382.9</v>
+        <v>36296.88</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1265,13 +1232,13 @@
         <v>16</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>6.38</v>
+        <v>7.25</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1684.32</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1297,13 +1264,13 @@
         <v>16</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1380</v>
+        <v>780</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7.7174</v>
+        <v>7.114</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>10650</v>
+        <v>5548.92</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1323,19 +1290,19 @@
         <v>14</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>6.85</v>
+        <v>7.83</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>4726.5</v>
+        <v>1096.2</v>
       </c>
     </row>
     <row r="22" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1355,19 +1322,19 @@
         <v>14</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5475</v>
+        <v>1452</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7.2248</v>
+        <v>10.0136</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>39555.51</v>
+        <v>14539.8</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1393,13 +1360,13 @@
         <v>16</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1240</v>
+        <v>462</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>6.7521</v>
+        <v>10.3</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>8372.6</v>
+        <v>4758.6</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1419,19 +1386,19 @@
         <v>14</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2080</v>
+        <v>2640</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.7255</v>
+        <v>10.1716</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>13989.04</v>
+        <v>26852.976</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1451,19 +1418,19 @@
         <v>14</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8.9</v>
+        <v>11.5992</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>854.4</v>
+        <v>579.96</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1483,19 +1450,19 @@
         <v>14</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1260</v>
+        <v>700</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.3926</v>
+        <v>13.6632</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8054.648</v>
+        <v>9564.24</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1515,19 +1482,19 @@
         <v>14</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>140</v>
+        <v>320</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4.61</v>
+        <v>15.5122</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>645.4</v>
+        <v>4963.888</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1547,19 +1514,19 @@
         <v>14</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1980</v>
+        <v>490</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.99</v>
+        <v>9.4814</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>19780.2</v>
+        <v>4645.9</v>
       </c>
     </row>
     <row r="29" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1579,19 +1546,19 @@
         <v>14</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>9.4667</v>
+        <v>12.166</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>3067.2</v>
+        <v>3649.8</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1617,13 +1584,13 @@
         <v>16</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5100</v>
+        <v>10200</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.9089</v>
+        <v>2.5</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>45435.6</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1643,19 +1610,19 @@
         <v>14</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>210</v>
+        <v>2400</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>11.9592</v>
+        <v>7.22</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>2511.432</v>
+        <v>17328</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1666,7 +1633,7 @@
         <v>76</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>13</v>
@@ -1681,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>64</v>
+        <v>21750</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12.21</v>
+        <v>4.9459</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>781.44</v>
+        <v>107572.5</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1695,10 +1662,10 @@
         <v>10</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>13</v>
@@ -1713,13 +1680,13 @@
         <v>16</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>450</v>
+        <v>33900</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>10.3716</v>
+        <v>4.1</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4667.2</v>
+        <v>138990</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1727,10 +1694,10 @@
         <v>10</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>13</v>
@@ -1745,13 +1712,13 @@
         <v>16</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>440</v>
+        <v>84450</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15.1418</v>
+        <v>4.2616</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6662.4</v>
+        <v>359888.64</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1759,10 +1726,10 @@
         <v>10</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>13</v>
@@ -1771,19 +1738,19 @@
         <v>14</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>35</v>
+        <v>10608</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>6.61</v>
+        <v>44.9497</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>231.35</v>
+        <v>476826.12</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1791,10 +1758,10 @@
         <v>10</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>13</v>
@@ -1803,19 +1770,19 @@
         <v>14</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3.5816</v>
+        <v>68.244</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>895.4</v>
+        <v>13921.776</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1823,10 +1790,10 @@
         <v>10</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>13</v>
@@ -1835,19 +1802,19 @@
         <v>14</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>210</v>
+        <v>816</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>9.8</v>
+        <v>47.5294</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2058</v>
+        <v>38784</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1855,10 +1822,10 @@
         <v>10</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>13</v>
@@ -1867,19 +1834,19 @@
         <v>14</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>35400</v>
+        <v>7272</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>2.5424</v>
+        <v>12.5124</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>90000</v>
+        <v>90990</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1887,10 +1854,10 @@
         <v>10</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>13</v>
@@ -1899,19 +1866,19 @@
         <v>14</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>10050</v>
+        <v>5796</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>5.18</v>
+        <v>13.2557</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>52059</v>
+        <v>76829.76</v>
       </c>
     </row>
     <row r="40" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1919,10 +1886,10 @@
         <v>10</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>13</v>
@@ -1931,19 +1898,19 @@
         <v>14</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>15000</v>
+        <v>324</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>4.1</v>
+        <v>11.19</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>61500</v>
+        <v>3625.56</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1951,10 +1918,10 @@
         <v>10</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>13</v>
@@ -1969,13 +1936,13 @@
         <v>16</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>38400</v>
+        <v>780</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>4.674</v>
+        <v>17</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>179483.1</v>
+        <v>13260</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -1983,10 +1950,10 @@
         <v>10</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>13</v>
@@ -2001,13 +1968,13 @@
         <v>16</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>8388</v>
+        <v>4020</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>41.8927</v>
+        <v>13.4</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>351396.0912</v>
+        <v>53868</v>
       </c>
     </row>
     <row r="43" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2015,10 +1982,10 @@
         <v>10</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>13</v>
@@ -2027,19 +1994,19 @@
         <v>14</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>41</v>
+        <v>13.4</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>14760</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="44" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2047,29 +2014,31 @@
         <v>10</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="4"/>
+      <c r="I44" s="4" t="n">
+        <v>29.88</v>
+      </c>
       <c r="J44" s="4" t="n">
-        <v>-466.3872</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2077,10 +2046,10 @@
         <v>10</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>13</v>
@@ -2089,19 +2058,19 @@
         <v>14</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1008</v>
+        <v>720</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>12.7</v>
+        <v>15</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>12801.6</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2109,10 +2078,10 @@
         <v>10</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>13</v>
@@ -2127,13 +2096,13 @@
         <v>16</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2916</v>
+        <v>2040</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13.4883</v>
+        <v>15.45</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>39331.7424</v>
+        <v>31518</v>
       </c>
     </row>
     <row r="47" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2141,10 +2110,10 @@
         <v>10</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>13</v>
@@ -2153,19 +2122,19 @@
         <v>14</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>10800</v>
+        <v>2160</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>12.57</v>
+        <v>13</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>135756</v>
+        <v>28080</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2173,10 +2142,10 @@
         <v>10</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>13</v>
@@ -2185,19 +2154,19 @@
         <v>14</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>18.85</v>
+        <v>107.44</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>11310</v>
+        <v>4512.48</v>
       </c>
     </row>
     <row r="49" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2205,10 +2174,10 @@
         <v>10</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>13</v>
@@ -2217,19 +2186,19 @@
         <v>14</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>15.44</v>
+        <v>31.68</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>926.4</v>
+        <v>633.6</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2237,10 +2206,10 @@
         <v>10</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>13</v>
@@ -2255,13 +2224,13 @@
         <v>16</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1500</v>
+        <v>14493</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13.9</v>
+        <v>13.0186</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>20850</v>
+        <v>188679</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2269,10 +2238,10 @@
         <v>10</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>13</v>
@@ -2287,13 +2256,13 @@
         <v>16</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>5004</v>
+        <v>600</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>11.99</v>
+        <v>19.8394</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>59997.96</v>
+        <v>11903.664</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2301,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>110</v>
@@ -2313,19 +2282,19 @@
         <v>14</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>4020</v>
+        <v>6350</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>15.9</v>
+        <v>20.79</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>63918</v>
+        <v>132016.5</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2333,10 +2302,10 @@
         <v>10</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>13</v>
@@ -2345,19 +2314,19 @@
         <v>14</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1476</v>
+        <v>43000</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>15.5</v>
+        <v>0.4221</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>22878</v>
+        <v>18150</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2365,10 +2334,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>13</v>
@@ -2383,13 +2352,13 @@
         <v>16</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>32.2608</v>
+        <v>0.29</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>16130.4</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2397,10 +2366,10 @@
         <v>10</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>13</v>
@@ -2409,19 +2378,19 @@
         <v>14</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>12930</v>
+        <v>10000</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>13.3155</v>
+        <v>0.62</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>172170</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2429,10 +2398,10 @@
         <v>10</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>13</v>
@@ -2447,13 +2416,13 @@
         <v>16</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>870</v>
+        <v>655000</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>19.852</v>
+        <v>0.3785</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>17271.264</v>
+        <v>247930</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2461,10 +2430,10 @@
         <v>10</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>13</v>
@@ -2473,19 +2442,19 @@
         <v>14</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>1675</v>
+        <v>6000</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>20.79</v>
+        <v>0.33</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>34823.25</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2493,10 +2462,10 @@
         <v>10</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>13</v>
@@ -2505,19 +2474,19 @@
         <v>14</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>100</v>
+        <v>13000</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>22.724</v>
+        <v>0.4785</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>2272.4</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2525,10 +2494,10 @@
         <v>10</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>13</v>
@@ -2537,19 +2506,19 @@
         <v>14</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>2700</v>
+        <v>100000</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>1944</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2557,10 +2526,10 @@
         <v>10</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>13</v>
@@ -2575,13 +2544,13 @@
         <v>16</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>194000</v>
+        <v>1985000</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.3722</v>
+        <v>0.3795</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>72214.8</v>
+        <v>753388.8</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2589,10 +2558,10 @@
         <v>10</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>13</v>
@@ -2601,19 +2570,19 @@
         <v>14</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.485</v>
+        <v>0.65</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>19400</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2621,10 +2590,10 @@
         <v>10</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>13</v>
@@ -2633,19 +2602,19 @@
         <v>14</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>10000</v>
+        <v>9936</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.59</v>
+        <v>6.4484</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>5900</v>
+        <v>64071.36</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2653,10 +2622,10 @@
         <v>10</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>13</v>
@@ -2665,19 +2634,19 @@
         <v>14</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>330000</v>
+        <v>1024</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>0.3885</v>
+        <v>14.5</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>128192.5</v>
+        <v>14848</v>
       </c>
     </row>
     <row r="64" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2685,10 +2654,10 @@
         <v>10</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>13</v>
@@ -2703,13 +2672,13 @@
         <v>16</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>22000</v>
+        <v>13080</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.4713</v>
+        <v>13.3584</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>10368</v>
+        <v>174727.6</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2717,10 +2686,10 @@
         <v>10</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>13</v>
@@ -2735,13 +2704,13 @@
         <v>16</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>1428000</v>
+        <v>5040</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0.3865</v>
+        <v>7.33</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>551960.8</v>
+        <v>36943.2</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2749,10 +2718,10 @@
         <v>10</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>13</v>
@@ -2761,19 +2730,19 @@
         <v>14</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>2700</v>
+        <v>50</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.78</v>
+        <v>14.5</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>2106</v>
+        <v>725</v>
       </c>
     </row>
     <row r="67" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2781,10 +2750,10 @@
         <v>10</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>13</v>
@@ -2793,19 +2762,19 @@
         <v>14</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>11304</v>
+        <v>224</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>6.5111</v>
+        <v>16.5</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>73602</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="68" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2813,10 +2782,10 @@
         <v>10</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>13</v>
@@ -2825,19 +2794,19 @@
         <v>14</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>9440</v>
+        <v>120</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>12.9554</v>
+        <v>10.27</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>122298.624</v>
+        <v>1232.4</v>
       </c>
     </row>
     <row r="69" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2845,10 +2814,10 @@
         <v>10</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>13</v>
@@ -2857,19 +2826,19 @@
         <v>14</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>500</v>
+        <v>2064</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>10.5</v>
+        <v>15.3818</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>5250</v>
+        <v>31748.096</v>
       </c>
     </row>
     <row r="70" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2877,10 +2846,10 @@
         <v>10</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>13</v>
@@ -2895,13 +2864,13 @@
         <v>16</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>11</v>
+        <v>11.49</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>33000</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="71" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2909,10 +2878,10 @@
         <v>10</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>13</v>
@@ -2927,13 +2896,13 @@
         <v>16</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>1568</v>
+        <v>3808</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>15.8174</v>
+        <v>16.8485</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>24801.664</v>
+        <v>64159.04</v>
       </c>
     </row>
     <row r="72" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2941,10 +2910,10 @@
         <v>10</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>13</v>
@@ -2953,19 +2922,19 @@
         <v>14</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>2272</v>
+        <v>240</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8.8577</v>
+        <v>30.77</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>20124.8</v>
+        <v>7384.8</v>
       </c>
     </row>
     <row r="73" customHeight="true" ht="16.5" customFormat="true" s="1">
@@ -2973,10 +2942,10 @@
         <v>10</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>13</v>
@@ -2991,191 +2960,31 @@
         <v>16</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>3024</v>
+        <v>1600</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>6.8433</v>
+        <v>12.9313</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>20694.24</v>
-      </c>
-    </row>
-    <row r="74" customHeight="true" ht="16.5" customFormat="true" s="1">
-      <c r="A74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I74" s="4" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="75" customHeight="true" ht="16.5" customFormat="true" s="1">
-      <c r="A75" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>3040</v>
-      </c>
-      <c r="I75" s="6" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>48336</v>
-      </c>
-    </row>
-    <row r="76" customHeight="true" ht="16.5" customFormat="true" s="1">
-      <c r="A76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>1408</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>17.4419</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>24558.1568</v>
-      </c>
-    </row>
-    <row r="77" customHeight="true" ht="16.5" customFormat="true" s="1">
-      <c r="A77" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>504</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>11944.8</v>
-      </c>
-    </row>
-    <row r="78" customHeight="true" ht="16.5" customFormat="true" s="1">
-      <c r="A78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>11376</v>
-      </c>
-    </row>
-    <row r="79" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="9" t="n">
-        <v>2254225</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>753.1783</v>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>2799581.8292</v>
+        <v>20690</v>
+      </c>
+    </row>
+    <row r="74" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A74" s="7"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="9" t="n">
+        <v>3110753</v>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>921.9094</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>3572290.936</v>
       </c>
     </row>
   </sheetData>
